--- a/data/trans_bre/IP07B_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP07B_R-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7,14</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-9,66</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-10,27</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24,37</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-13,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-11,98%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>49,59%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>7.140525479595028</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-9.66211908584339</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-10.27455296390245</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>24.37169165040779</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1056810264861848</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.1340996309669141</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.1197833860846796</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.4959280363954223</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-7,75; 22,87</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-24,93; 4,95</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-26,24; 5,92</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-6,13; 53,55</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-10,01; 41,23</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-32,23; 7,58</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-29,41; 7,8</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-9,91; 191,17</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-7.75346694384189</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-24.93261560629407</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-26.24320838727463</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-6.12928902821928</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.100139761314548</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.3223347530506334</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.2940915280380706</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.09906392208312038</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>22.87439708229492</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.945962944359576</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.915484279395971</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>53.55345970335951</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.4123106755188006</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.07578842802219085</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.07804095689901831</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.911730551062794</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,33</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3,46</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,97</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,29</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-4,42; 9,72</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,3; 10,37</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,67; 8,26</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-5,59; 16,51</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-5,74; 13,83</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-5,62; 15,23</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-4,39; 10,3</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-8,52; 30,43</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>2.333057655815984</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.455508911042637</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.966212059955086</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>4.294768940544524</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.03144005416836736</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.04744054606795145</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.02389046298643737</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.06967669356344923</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-2,78</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-7,34</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,97</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,07</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,24%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-10,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18,56%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-4.422106119927926</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.304102631427434</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.669392688223909</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-5.586726479640626</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.05740360813281526</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.05621487881443853</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.0438545986567986</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.08515054222659581</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-14,63; 8,5</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-21,05; 8,01</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-3,27; 18,11</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-6,13; 27,67</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-16,15; 10,45</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-27,16; 13,2</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-3,77; 24,54</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-9,07; 55,46</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>9.721052511016481</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>10.36755597391871</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>8.264585769918506</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>16.509593926106</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1382711469556832</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.1523360418093967</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.1030119911372939</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.3043372971750883</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,33</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,91</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,98</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-1,27%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.776228851249807</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-7.336867816216608</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>6.969101359115292</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>11.07192507603335</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.0324483470267763</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1042740369020284</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.08657246407575377</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.1855972003445413</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,29; 7,84</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-6,89; 5,14</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,63; 6,44</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,39; 16,11</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-4,13; 10,75</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-9,15; 7,39</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-4,41; 8,13</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-2,17; 29,83</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-14.63461293273619</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-21.04898762565644</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.271549243509186</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.132634692380497</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1615000498802776</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.2715790495687894</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.03774977974537365</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.09066857274881393</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.499679738231425</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.008324317930965</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>18.11215158870325</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>27.67485196575744</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1045252904834166</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1319867206133141</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.2453533818210131</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.5545914273959358</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2.33469743258008</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.9148064283611035</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.846761306379352</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>6.977610046085503</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.03109063332127218</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.01265204131418883</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.02244353353207117</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.1153746121960451</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.288548727368842</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-6.890190382440007</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.63181690645994</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.391655288408511</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.04126254752211242</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.09151345240261692</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.04407075446241911</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.02166209500842432</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.838969169407325</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.144292900070104</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.442120832788077</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>16.10560359550835</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1075143071863551</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.07391672575594196</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.08127743754118168</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.2982686769489881</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
